--- a/artfynd/A 15913-2026 artfynd.xlsx
+++ b/artfynd/A 15913-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1383,6 +1383,549 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132830916</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>697347</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6643725</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132830917</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>697335</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6643723</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132830920</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>697224</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6643706</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132830919</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>697303</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6643744</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132830921</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>697167</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6643826</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15913-2026 artfynd.xlsx
+++ b/artfynd/A 15913-2026 artfynd.xlsx
@@ -1388,7 +1388,7 @@
         <v>132830916</v>
       </c>
       <c r="B8" t="n">
-        <v>99153</v>
+        <v>99154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>132830917</v>
       </c>
       <c r="B9" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>132830920</v>
       </c>
       <c r="B10" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>132830919</v>
       </c>
       <c r="B11" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>132830921</v>
       </c>
       <c r="B12" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 15913-2026 artfynd.xlsx
+++ b/artfynd/A 15913-2026 artfynd.xlsx
@@ -1388,7 +1388,7 @@
         <v>132830916</v>
       </c>
       <c r="B8" t="n">
-        <v>99154</v>
+        <v>99156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>132830917</v>
       </c>
       <c r="B9" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,53 +1599,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132830920</v>
+        <v>132830919</v>
       </c>
       <c r="B10" t="n">
-        <v>58115</v>
+        <v>101329</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697224</v>
+        <v>697303</v>
       </c>
       <c r="R10" t="n">
-        <v>6643706</v>
+        <v>6643744</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1687,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,45 +1706,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132830919</v>
+        <v>132830920</v>
       </c>
       <c r="B11" t="n">
-        <v>101327</v>
+        <v>58115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697303</v>
+        <v>697224</v>
       </c>
       <c r="R11" t="n">
-        <v>6643744</v>
+        <v>6643706</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,7 +1824,7 @@
         <v>132830921</v>
       </c>
       <c r="B12" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 15913-2026 artfynd.xlsx
+++ b/artfynd/A 15913-2026 artfynd.xlsx
@@ -1388,7 +1388,7 @@
         <v>132830916</v>
       </c>
       <c r="B8" t="n">
-        <v>99156</v>
+        <v>99157</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>132830917</v>
       </c>
       <c r="B9" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>132830919</v>
       </c>
       <c r="B10" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>132830921</v>
       </c>
       <c r="B12" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 15913-2026 artfynd.xlsx
+++ b/artfynd/A 15913-2026 artfynd.xlsx
@@ -1599,45 +1599,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132830919</v>
+        <v>132830920</v>
       </c>
       <c r="B10" t="n">
-        <v>101330</v>
+        <v>58115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697303</v>
+        <v>697224</v>
       </c>
       <c r="R10" t="n">
-        <v>6643744</v>
+        <v>6643706</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1687,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,53 +1714,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132830920</v>
+        <v>132830919</v>
       </c>
       <c r="B11" t="n">
-        <v>58115</v>
+        <v>101330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697224</v>
+        <v>697303</v>
       </c>
       <c r="R11" t="n">
-        <v>6643706</v>
+        <v>6643744</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15913-2026 artfynd.xlsx
+++ b/artfynd/A 15913-2026 artfynd.xlsx
@@ -1599,53 +1599,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132830920</v>
+        <v>132830919</v>
       </c>
       <c r="B10" t="n">
-        <v>58115</v>
+        <v>101330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697224</v>
+        <v>697303</v>
       </c>
       <c r="R10" t="n">
-        <v>6643706</v>
+        <v>6643744</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1687,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,45 +1706,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132830919</v>
+        <v>132830920</v>
       </c>
       <c r="B11" t="n">
-        <v>101330</v>
+        <v>58115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697303</v>
+        <v>697224</v>
       </c>
       <c r="R11" t="n">
-        <v>6643744</v>
+        <v>6643706</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15913-2026 artfynd.xlsx
+++ b/artfynd/A 15913-2026 artfynd.xlsx
@@ -1388,7 +1388,7 @@
         <v>132830916</v>
       </c>
       <c r="B8" t="n">
-        <v>99157</v>
+        <v>99160</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>132830917</v>
       </c>
       <c r="B9" t="n">
-        <v>101330</v>
+        <v>101333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>132830919</v>
       </c>
       <c r="B10" t="n">
-        <v>101330</v>
+        <v>101333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>132830920</v>
       </c>
       <c r="B11" t="n">
-        <v>58115</v>
+        <v>58118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>132830921</v>
       </c>
       <c r="B12" t="n">
-        <v>101330</v>
+        <v>101333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 15913-2026 artfynd.xlsx
+++ b/artfynd/A 15913-2026 artfynd.xlsx
@@ -1599,45 +1599,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132830919</v>
+        <v>132830920</v>
       </c>
       <c r="B10" t="n">
-        <v>101333</v>
+        <v>58118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697303</v>
+        <v>697224</v>
       </c>
       <c r="R10" t="n">
-        <v>6643744</v>
+        <v>6643706</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1687,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,53 +1714,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132830920</v>
+        <v>132830919</v>
       </c>
       <c r="B11" t="n">
-        <v>58118</v>
+        <v>101333</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697224</v>
+        <v>697303</v>
       </c>
       <c r="R11" t="n">
-        <v>6643706</v>
+        <v>6643744</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15913-2026 artfynd.xlsx
+++ b/artfynd/A 15913-2026 artfynd.xlsx
@@ -1388,7 +1388,7 @@
         <v>132830916</v>
       </c>
       <c r="B8" t="n">
-        <v>99160</v>
+        <v>99161</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>132830917</v>
       </c>
       <c r="B9" t="n">
-        <v>101333</v>
+        <v>101334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>132830919</v>
       </c>
       <c r="B11" t="n">
-        <v>101333</v>
+        <v>101334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>132830921</v>
       </c>
       <c r="B12" t="n">
-        <v>101333</v>
+        <v>101334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 15913-2026 artfynd.xlsx
+++ b/artfynd/A 15913-2026 artfynd.xlsx
@@ -1388,7 +1388,7 @@
         <v>132830916</v>
       </c>
       <c r="B8" t="n">
-        <v>99161</v>
+        <v>99165</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>132830917</v>
       </c>
       <c r="B9" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>132830920</v>
       </c>
       <c r="B10" t="n">
-        <v>58118</v>
+        <v>58119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>132830919</v>
       </c>
       <c r="B11" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>132830921</v>
       </c>
       <c r="B12" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 15913-2026 artfynd.xlsx
+++ b/artfynd/A 15913-2026 artfynd.xlsx
@@ -1599,53 +1599,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132830920</v>
+        <v>132830919</v>
       </c>
       <c r="B10" t="n">
-        <v>58119</v>
+        <v>101338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697224</v>
+        <v>697303</v>
       </c>
       <c r="R10" t="n">
-        <v>6643706</v>
+        <v>6643744</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1687,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,45 +1706,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132830919</v>
+        <v>132830920</v>
       </c>
       <c r="B11" t="n">
-        <v>101338</v>
+        <v>58119</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697303</v>
+        <v>697224</v>
       </c>
       <c r="R11" t="n">
-        <v>6643744</v>
+        <v>6643706</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15913-2026 artfynd.xlsx
+++ b/artfynd/A 15913-2026 artfynd.xlsx
@@ -1599,45 +1599,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132830919</v>
+        <v>132830920</v>
       </c>
       <c r="B10" t="n">
-        <v>101338</v>
+        <v>58119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697303</v>
+        <v>697224</v>
       </c>
       <c r="R10" t="n">
-        <v>6643744</v>
+        <v>6643706</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1687,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,53 +1714,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132830920</v>
+        <v>132830919</v>
       </c>
       <c r="B11" t="n">
-        <v>58119</v>
+        <v>101338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697224</v>
+        <v>697303</v>
       </c>
       <c r="R11" t="n">
-        <v>6643706</v>
+        <v>6643744</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15913-2026 artfynd.xlsx
+++ b/artfynd/A 15913-2026 artfynd.xlsx
@@ -1388,7 +1388,7 @@
         <v>132830916</v>
       </c>
       <c r="B8" t="n">
-        <v>99165</v>
+        <v>99167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>132830917</v>
       </c>
       <c r="B9" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,45 +1599,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132830919</v>
+        <v>132830920</v>
       </c>
       <c r="B10" t="n">
-        <v>101338</v>
+        <v>58119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697303</v>
+        <v>697224</v>
       </c>
       <c r="R10" t="n">
-        <v>6643744</v>
+        <v>6643706</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1687,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,53 +1714,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132830920</v>
+        <v>132830919</v>
       </c>
       <c r="B11" t="n">
-        <v>58119</v>
+        <v>101340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697224</v>
+        <v>697303</v>
       </c>
       <c r="R11" t="n">
-        <v>6643706</v>
+        <v>6643744</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,7 +1824,7 @@
         <v>132830921</v>
       </c>
       <c r="B12" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 15913-2026 artfynd.xlsx
+++ b/artfynd/A 15913-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>55545706</v>
       </c>
       <c r="B2" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697162.7707500386</v>
+        <v>697163</v>
       </c>
       <c r="R2" t="n">
-        <v>6643833.906990616</v>
+        <v>6643834</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,19 +745,9 @@
           <t>2015-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,53 +780,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55545746</v>
+        <v>55545709</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Eklund, ONO om, Upl</t>
+          <t>Eklund, NO om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697434.926845592</v>
+        <v>697190</v>
       </c>
       <c r="R3" t="n">
-        <v>6643718.159720743</v>
+        <v>6643818</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,19 +850,14 @@
           <t>2015-10-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-10-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog på delvis kalkhaltig mark.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,6 +866,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -910,19 +885,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55545709</v>
+        <v>55545747</v>
       </c>
       <c r="B4" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -935,12 +905,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,14 +918,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Eklund, NO om, Upl</t>
+          <t>Eklund, ONO om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697189.8267876098</v>
+        <v>697347</v>
       </c>
       <c r="R4" t="n">
-        <v>6643817.746720972</v>
+        <v>6643651</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,24 +955,9 @@
           <t>2015-10-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-10-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog på delvis kalkhaltig mark.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,56 +985,56 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55545744</v>
+        <v>132830920</v>
       </c>
       <c r="B5" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Eklund, ONO om, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697434.926845592</v>
+        <v>697224</v>
       </c>
       <c r="R5" t="n">
-        <v>6643718.159720743</v>
+        <v>6643706</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,27 +1058,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Blockrik mark med gammal rötskadad asp gammal tall och olikåldrig gran.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,27 +1088,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>55545747</v>
+        <v>55545744</v>
       </c>
       <c r="B6" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,36 +1111,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Eklund, ONO om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697346.8155027893</v>
+        <v>697435</v>
       </c>
       <c r="R6" t="n">
-        <v>6643651.098782958</v>
+        <v>6643718</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1225,19 +1171,14 @@
           <t>2015-10-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-10-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Blockrik mark med gammal rötskadad asp gammal tall och olikåldrig gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,7 +1187,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1265,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>55545707</v>
+        <v>132830916</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99230</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,40 +1216,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Eklund, NO om, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697162.7707500386</v>
+        <v>697347</v>
       </c>
       <c r="R7" t="n">
-        <v>6643833.906990616</v>
+        <v>6643725</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,27 +1270,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog på delvis kalkhaltig mark.</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,57 +1300,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132830916</v>
+        <v>132824392</v>
       </c>
       <c r="B8" t="n">
-        <v>99167</v>
+        <v>99195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697347</v>
+        <v>697135</v>
       </c>
       <c r="R8" t="n">
-        <v>6643725</v>
+        <v>6643852</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,60 +1416,63 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132830917</v>
+        <v>55545731</v>
       </c>
       <c r="B9" t="n">
-        <v>101340</v>
+        <v>102241</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, ONO om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697335</v>
+        <v>697337</v>
       </c>
       <c r="R9" t="n">
-        <v>6643723</v>
+        <v>6643765</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,22 +1496,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Blockrik mark med gammal rötskadad asp gammal tall och olikåldrig gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,68 +1521,63 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132830920</v>
+        <v>55545707</v>
       </c>
       <c r="B10" t="n">
-        <v>58119</v>
+        <v>101326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, NO om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697224</v>
+        <v>697163</v>
       </c>
       <c r="R10" t="n">
-        <v>6643706</v>
+        <v>6643834</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1672,22 +1601,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:05</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:05</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog på delvis kalkhaltig mark.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,22 +1626,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132830919</v>
+        <v>55545733</v>
       </c>
       <c r="B11" t="n">
-        <v>101340</v>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,19 +1667,22 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, ONO om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697303</v>
+        <v>697337</v>
       </c>
       <c r="R11" t="n">
-        <v>6643744</v>
+        <v>6643765</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1779,22 +1706,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,22 +1726,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132830921</v>
+        <v>55545746</v>
       </c>
       <c r="B12" t="n">
-        <v>101340</v>
+        <v>101326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,19 +1767,22 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, ONO om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697167</v>
+        <v>697435</v>
       </c>
       <c r="R12" t="n">
-        <v>6643826</v>
+        <v>6643718</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1886,22 +1806,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,15 +1826,336 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132830917</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>697335</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6643723</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132830919</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>697303</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6643744</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132830921</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>697167</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6643826</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15913-2026 artfynd.xlsx
+++ b/artfynd/A 15913-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545706</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545709</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545747</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830920</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545744</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830916</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132824392</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1530,6 +1570,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545731</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545707</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1735,6 +1785,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545733</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1835,6 +1890,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545746</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1942,6 +2002,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830917</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2049,6 +2114,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830919</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,8 +2226,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830921</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>